--- a/IBOARDConnector.xlsx
+++ b/IBOARDConnector.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Software\GitHub\PiSubmarine\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851A0370-F2F5-4345-8885-041EB7B3D722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{737CB079-F84C-47AE-8358-3C17FCD3DFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,9 +63,6 @@
     <t>I2C_CHG_SDA</t>
   </si>
   <si>
-    <t>Hong Cheng HC-PM254-8.5H-2x8PS</t>
-  </si>
-  <si>
     <t>INCP IPCP254M16PB28S</t>
   </si>
   <si>
@@ -85,6 +82,9 @@
   </si>
   <si>
     <t>3.3V 2A</t>
+  </si>
+  <si>
+    <t>HC-PM254-8.5H-2x10PS</t>
   </si>
 </sst>
 </file>
@@ -516,10 +516,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -536,7 +536,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
         <v>1</v>
@@ -544,16 +544,16 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -580,7 +580,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -593,10 +593,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
